--- a/data/raw_erp_export.xlsx
+++ b/data/raw_erp_export.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37594.07</v>
+        <v>28837.52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>43988.11</v>
+        <v>17747.13</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46341.11</v>
+        <v>17350.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31424.83</v>
+        <v>29528.22</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46472.72</v>
+        <v>25488.43</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37755.88</v>
+        <v>28064.14</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>42992.63</v>
+        <v>21544.21</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>29175.47</v>
+        <v>25363.49</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35804.74</v>
+        <v>19654.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>42498.11</v>
+        <v>20207.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -933,20 +933,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>4000</t>
@@ -958,7 +962,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>27744.97</v>
+        <v>21080.39</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -974,20 +978,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>4000</t>
@@ -999,7 +1007,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>27404.98</v>
+        <v>16901.91</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1015,20 +1023,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1040,7 +1052,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>26112.55</v>
+        <v>18062.06</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1056,20 +1068,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1081,7 +1097,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>31237.83</v>
+        <v>26284.76</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1097,20 +1113,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1122,7 +1142,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>37676.24</v>
+        <v>22705.66</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1138,20 +1158,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>US05</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1163,7 +1187,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>43044.33</v>
+        <v>24790.72</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1179,7 +1203,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1204,7 +1228,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32434.31</v>
+        <v>26846.51</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1245,7 +1269,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>33275.75</v>
+        <v>15559.05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1261,7 +1285,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1286,7 +1310,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>31517.67</v>
+        <v>18347.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1302,7 +1326,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1327,7 +1351,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31870.78</v>
+        <v>27685.8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1343,12 +1367,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1368,7 +1392,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>42111.23</v>
+        <v>21816.76</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1384,12 +1408,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1409,7 +1433,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>37160.14</v>
+        <v>28620.06</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1425,12 +1449,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1450,7 +1474,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>30866.46</v>
+        <v>20849.49</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1466,12 +1490,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1491,7 +1515,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>27589.59</v>
+        <v>16525.39</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1507,12 +1531,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1528,11 +1552,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-4554.92</v>
+        <v>23942.48</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1548,24 +1572,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1577,7 +1597,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60278.22</v>
+        <v>25929.41</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1593,24 +1613,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1622,7 +1638,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>43459.56</v>
+        <v>19147.92</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1638,24 +1654,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1667,7 +1679,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>38288.18</v>
+        <v>16713.42</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1683,24 +1695,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1712,7 +1720,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>34981.93</v>
+        <v>19985.18</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1728,24 +1736,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1757,7 +1761,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>45964.06</v>
+        <v>28403.01</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1773,24 +1777,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>38381.96</v>
+        <v>25656.54</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1818,24 +1818,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1847,7 +1843,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>59129.2</v>
+        <v>17124.62</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1863,24 +1859,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>4000</t>
@@ -1892,7 +1884,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>59604.31</v>
+        <v>18836.16</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1908,17 +1900,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>US05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1933,11 +1925,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>34097.28</v>
+        <v>16898.74</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1941,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>US05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1974,11 +1966,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>27783.56</v>
+        <v>16350.17</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1990,17 +1982,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>US05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2015,11 +2007,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>25042.83</v>
+        <v>26176.15</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2031,17 +2023,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Gutschrift Retoure Grosshandel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>US05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2052,15 +2044,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Credit Note</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>26326.32</v>
+        <v>-4271.43</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2072,20 +2064,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2097,11 +2093,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>23298.44</v>
+        <v>22752.31</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2113,20 +2109,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2138,11 +2138,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>38129.17</v>
+        <v>14915.94</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2154,20 +2154,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2179,11 +2183,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>36046.71</v>
+        <v>19371.96</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2195,20 +2199,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2220,11 +2228,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>31259.62</v>
+        <v>22570.14</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2236,20 +2244,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2261,11 +2273,11 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>26329.4</v>
+        <v>16325.45</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2277,20 +2289,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2302,11 +2318,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>35264.07</v>
+        <v>22130.07</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2318,20 +2334,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2343,11 +2363,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>39089.12</v>
+        <v>25222.43</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2359,20 +2379,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2384,11 +2408,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>24441.1</v>
+        <v>16432.91</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2400,20 +2424,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2425,11 +2453,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>42057.35</v>
+        <v>19591.78</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2441,20 +2469,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2466,11 +2498,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>40811.88</v>
+        <v>22634.43</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2482,20 +2514,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>DE01</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2503,15 +2539,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-4455.22</v>
+        <v>18641.87</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2559,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2538,7 +2574,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2552,7 +2588,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>49196.9</v>
+        <v>17601.85</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2568,12 +2604,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2583,7 +2619,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2597,7 +2633,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>50890.47</v>
+        <v>22422.46</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2613,12 +2649,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2628,7 +2664,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2642,7 +2678,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47103.33</v>
+        <v>23872.77</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2658,12 +2694,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2673,7 +2709,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2687,7 +2723,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>51625.82</v>
+        <v>16719.8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2703,12 +2739,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2718,7 +2754,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2732,7 +2768,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>34468.27</v>
+        <v>22656.29</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2748,12 +2784,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2763,7 +2799,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2777,7 +2813,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>36050.63</v>
+        <v>21709.4</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2793,12 +2829,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2808,7 +2844,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2822,7 +2858,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>28515.76</v>
+        <v>23388.05</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2838,12 +2874,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2853,7 +2889,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2867,7 +2903,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>50866.23</v>
+        <v>19618.44</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2883,12 +2919,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2898,7 +2934,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2912,7 +2948,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>45896.96</v>
+        <v>20808.32</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2928,17 +2964,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2953,7 +2989,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>37500.59</v>
+        <v>19360.5</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2969,17 +3005,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2994,7 +3030,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>33091.36</v>
+        <v>21409.6</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3010,17 +3046,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3035,7 +3071,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37287.65</v>
+        <v>20966.9</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3051,17 +3087,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3076,7 +3112,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>34276.06</v>
+        <v>14594.85</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3092,17 +3128,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3117,7 +3153,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>34612.38</v>
+        <v>16221.12</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3133,17 +3169,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3158,7 +3194,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>34014.71</v>
+        <v>24484.77</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3174,17 +3210,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3199,7 +3235,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>29426.64</v>
+        <v>22532.65</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3215,17 +3251,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3240,7 +3276,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>41502.21</v>
+        <v>14536.21</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3256,17 +3292,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3281,7 +3317,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>25178.73</v>
+        <v>18562.15</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3297,17 +3333,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3322,7 +3358,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>41057.39</v>
+        <v>16652.38</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3338,17 +3374,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3363,7 +3399,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>40793.11</v>
+        <v>14270.9</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3379,17 +3415,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3404,7 +3440,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>33445.65</v>
+        <v>17039.34</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3420,17 +3456,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3445,7 +3481,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>39054.68</v>
+        <v>19968.66</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3461,17 +3497,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FR03</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3482,11 +3518,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>-4566.74</v>
+        <v>25168.36</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3502,24 +3538,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3531,11 +3563,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>35196.5</v>
+        <v>14807.19</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3547,24 +3579,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3576,11 +3604,11 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>26928.83</v>
+        <v>15350.8</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3592,24 +3620,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3621,11 +3645,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>34358.36</v>
+        <v>19019.93</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3637,24 +3661,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3666,11 +3686,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>27151.08</v>
+        <v>17615.73</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3682,24 +3702,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3711,11 +3727,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>36536.7</v>
+        <v>22343.51</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3727,24 +3743,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3756,11 +3768,11 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>33924.22</v>
+        <v>19862.04</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3772,24 +3784,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3801,11 +3809,11 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>42699.43</v>
+        <v>24860.06</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3817,24 +3825,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3846,11 +3850,11 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>30068.29</v>
+        <v>20661.14</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3862,24 +3866,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3891,11 +3891,11 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>42542.92</v>
+        <v>24586.39</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3907,17 +3907,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Gutschrift Retoure Grosshandel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SG01</t>
+          <t>DE01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3928,15 +3928,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Credit Note</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>31033.51</v>
+        <v>-4404.7</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -3948,20 +3948,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>4000</t>
@@ -3973,11 +3977,11 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>32050.58</v>
+        <v>26567.23</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -3989,20 +3993,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4014,11 +4022,11 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>34882.65</v>
+        <v>21803.44</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4030,20 +4038,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4055,11 +4067,11 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>24136.4</v>
+        <v>26663</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4071,20 +4083,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4096,11 +4112,11 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>30026.51</v>
+        <v>24502.64</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4112,20 +4128,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4137,11 +4157,11 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>31850.24</v>
+        <v>22533.72</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4153,20 +4173,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4178,11 +4202,11 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>27376.41</v>
+        <v>28111.77</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4194,20 +4218,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4219,11 +4247,11 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>38573.8</v>
+        <v>17532.02</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4235,20 +4263,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4260,11 +4292,11 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>32098.71</v>
+        <v>26875.72</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4276,20 +4308,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4301,11 +4337,11 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>33383.48</v>
+        <v>16775.01</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4317,20 +4353,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4342,11 +4382,11 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>31745.78</v>
+        <v>24787.71</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4358,20 +4398,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4383,11 +4427,11 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21639.84</v>
+        <v>23100.63</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4399,20 +4443,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4420,15 +4468,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>-3651.46</v>
+        <v>19585.18</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4440,27 +4488,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4469,11 +4517,11 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>130988.44</v>
+        <v>26148.4</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4485,27 +4533,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4514,11 +4562,11 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>132529.4</v>
+        <v>23329.08</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4530,27 +4578,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4559,11 +4607,11 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>118130.82</v>
+        <v>24973.03</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4575,27 +4623,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4604,11 +4652,11 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>85283.12</v>
+        <v>29262.78</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4620,27 +4668,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4649,11 +4697,11 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>107659.98</v>
+        <v>19944.23</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4665,27 +4713,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4694,11 +4742,11 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>129257.69</v>
+        <v>16515.87</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4758,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q1 2025 - US05</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4725,12 +4773,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>US05</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4739,7 +4787,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2146.79</v>
+        <v>20578</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4755,27 +4803,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q2 2025 - US05</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>US05</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4784,11 +4828,11 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1903.98</v>
+        <v>14863.83</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -4800,27 +4844,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q3 2025 - US05</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>US05</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4829,11 +4869,11 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2131.37</v>
+        <v>22382.65</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -4845,27 +4885,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q4 2025 - US05</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>US05</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4874,11 +4910,11 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2168.94</v>
+        <v>14759.99</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -4890,27 +4926,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q1 2025 - DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4919,11 +4951,11 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>2213.74</v>
+        <v>13952.17</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -4935,27 +4967,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q2 2025 - DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4964,11 +4992,11 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1942.53</v>
+        <v>16270.26</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -4980,27 +5008,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q3 2025 - DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5009,11 +5033,11 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2189.58</v>
+        <v>22112.97</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5025,27 +5049,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q4 2025 - DE01</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>DE01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5054,11 +5074,11 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>2015.69</v>
+        <v>12944.48</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5070,27 +5090,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q1 2025 - FR03</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
           <t>FR03</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5099,11 +5115,11 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>4046.3</v>
+        <v>13197.17</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5115,27 +5131,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q2 2025 - FR03</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
           <t>FR03</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5144,11 +5156,11 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>4180.04</v>
+        <v>23021.23</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5160,27 +5172,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q3 2025 - FR03</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
           <t>FR03</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5189,11 +5197,11 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>4272.77</v>
+        <v>21321.71</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5205,27 +5213,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q4 2025 - FR03</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
           <t>FR03</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5234,11 +5238,11 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3941.17</v>
+        <v>13719.24</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5250,27 +5254,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q1 2025 - SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5279,11 +5279,11 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2242.07</v>
+        <v>17563.45</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5295,27 +5295,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q2 2025 - SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5324,11 +5320,11 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2009.03</v>
+        <v>22435.49</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5340,27 +5336,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q3 2025 - SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5369,11 +5361,11 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>2252.01</v>
+        <v>21418.63</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5385,27 +5377,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Marke/Patent Q4 2025 - SG01</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5414,11 +5402,11 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1872.19</v>
+        <v>16611.27</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5430,27 +5418,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Herstellungs-Know-how Q1 2025 - CH04</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5459,11 +5443,11 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3535.07</v>
+        <v>18084.81</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5475,27 +5459,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Herstellungs-Know-how Q2 2025 - CH04</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5504,11 +5484,11 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>3371.58</v>
+        <v>19716.46</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5520,27 +5500,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Herstellungs-Know-how Q3 2025 - CH04</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5549,11 +5525,11 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>3631.92</v>
+        <v>20189.63</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5565,27 +5541,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lizenzgebuehr Herstellungs-Know-how Q4 2025 - CH04</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5594,11 +5566,11 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>3345.53</v>
+        <v>21536.64</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5610,40 +5582,36 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CH04</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
           <t>FR03</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4910.19</v>
+        <v>19208.53</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5655,36 +5623,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DE01</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>US02</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>2078.82</v>
+        <v>15944.32</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -5700,36 +5664,36 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>US02</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>363.82</v>
+        <v>21395.37</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5741,36 +5705,36 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SG01</t>
+          <t>FR03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3602.26</v>
+        <v>15491.59</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5782,40 +5746,36 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CH04</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>SG01</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>4922.98</v>
+        <v>19023.87</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5827,27 +5787,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>US02</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5856,11 +5812,11 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2232.77</v>
+        <v>19781.95</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5872,27 +5828,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>US05</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>US02</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5901,11 +5853,11 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3179.09</v>
+        <v>15523.18</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5917,27 +5869,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Gutschrift Retoure Grosshandel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SG01</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5946,11 +5894,11 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>4289.28</v>
+        <v>-4677.93</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -5962,40 +5910,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>SG01</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>US05</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2265.47</v>
+        <v>10569.62</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -6007,27 +5955,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>SG01</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>US02</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6036,11 +5984,11 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1256.96</v>
+        <v>11691.77</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -6052,27 +6000,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>SG01</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -6081,11 +6029,11 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>3401.87</v>
+        <v>13547.2</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -6097,27 +6045,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>US05</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>SG01</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -6126,7 +6074,7 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>731.86</v>
+        <v>10069.04</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6142,12 +6090,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6155,10 +6103,14 @@
           <t>US02</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -6167,7 +6119,7 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2488.96</v>
+        <v>11321.65</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6183,36 +6135,36 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>US05</t>
+          <t>US02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>DE01</t>
+          <t>SG01</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Credit Note</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2814.21</v>
+        <v>13347.29</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6228,27 +6180,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>SG01</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>US02</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6257,11 +6209,11 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>4402.62</v>
+        <v>12808.74</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -6273,36 +6225,3430 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>13770.91</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TX00136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>10635.98</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TX00137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>11859.91</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TX00138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>8947.57</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TX00139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>12320.56</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TX00140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>12949.51</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TX00141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>11796.59</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TX00142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>12292.68</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TX00143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>9002.379999999999</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TX00144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>13482.08</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TX00145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>14007.3</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TX00146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>13986.86</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TX00147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>15835.06</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TX00148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>17264.69</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TX00149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>19401.98</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TX00150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>15252.26</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TX00151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>20182.81</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TX00152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>19258.14</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TX00153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>15696.16</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TX00154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>17183.67</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TX00155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>14969.06</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TX00156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>19065.97</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TX00157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>16262</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TX00158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>17287.79</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TX00159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>17928.5</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TX00160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>14962.16</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TX00161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>16074.04</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TX00162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>18611.55</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TX00163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>16099.72</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TX00164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>12399.62</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TX00165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>15658.92</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TX00166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>19320.04</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TX00167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>13258.2</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TX00168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>17122.29</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TX00169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Gutschrift Retoure Grosshandel</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>-3654.4</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TX00170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>56778.6</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TX00171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>74606.83</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TX00172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>87457.23</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TX00173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>54186.98</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TX00174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>81354.19</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TX00175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>49727.22</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TX00176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>56889.59</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TX00177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>58275.6</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>TX00178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>77497.32000000001</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TX00179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>62239.84</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TX00180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>63630.54</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TX00181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Lohnfertigungsgebuehr API-Produktion</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>74685.07000000001</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TX00182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
           <t>Sonstige Kosten - noch nicht klassifiziert</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>2184.33</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TX00183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>2763.22</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TX00184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
         <is>
           <t>SG01</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>4900</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>540.1</v>
-      </c>
-      <c r="I136" t="inlineStr">
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>3136.21</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TX00185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>4090.44</v>
+      </c>
+      <c r="I186" t="inlineStr">
         <is>
           <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TX00186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>4475.08</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TX00187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>842.87</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TX00188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>1445.59</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TX00189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>3991.69</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TX00190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>3489.03</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TX00191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>3475.44</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TX00192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>3246.38</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TX00193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>4053.65</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TX00194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>3857.59</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TX00195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>751.75</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TX00196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>657.1799999999999</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TX00197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>572.51</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TX00198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>2246.93</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TX00199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>1991.14</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TX00200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>2378.96</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TX00201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>992.37</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TX00202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>4403.01</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TX00203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>2620.59</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TX00204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>3773.29</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TX00205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>4423.24</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TX00206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>1192.78</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TX00207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>2450.43</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TX00208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>437.94</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TX00209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>US05</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>1237.03</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TX00210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>SG01</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>568.8</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TX00211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Credit Note</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>774.13</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TX00212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>US02</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>3153.9</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TX00213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DE01</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>FR03</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>4900</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>2622.85</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
     </row>

--- a/data/raw_erp_export.xlsx
+++ b/data/raw_erp_export.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft US05</t>
+          <t>Sale of finished pharmaceuticals to distributor US05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
+          <t>Sale of finished goods to wholesaler Cardinal Health East</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Cardinal Health East</t>
+          <t>Sale of finished goods to wholesaler Cardinal Health East</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler AmerisourceBergen Pharma</t>
+          <t>Sale of finished goods to wholesaler AmerisourceBergen Pharma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler McKesson Specialty Distribution</t>
+          <t>Sale of finished goods to wholesaler McKesson Specialty Distribution</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Credit note wholesale return</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft DE01</t>
+          <t>Sale of finished pharmaceuticals to distributor DE01</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Apothekengenossenschaft Nord</t>
+          <t>Sale of finished goods to wholesaler Apothekengenossenschaft Nord</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Phoenix Pharmahandel AG</t>
+          <t>Sale of finished goods to wholesaler Phoenix Pharmahandel AG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler MedGross Deutschland</t>
+          <t>Sale of finished goods to wholesaler MedGross Deutschland</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Credit note wholesale return</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft FR03</t>
+          <t>Sale of finished pharmaceuticals to distributor FR03</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Pharmacie Centrale Lyon</t>
+          <t>Sale of finished goods to wholesaler Pharmacie Centrale Lyon</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler CERP Rouen Distribution</t>
+          <t>Sale of finished goods to wholesaler CERP Rouen Distribution</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler OCP Pharma France</t>
+          <t>Sale of finished goods to wholesaler OCP Pharma France</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Credit note wholesale return</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Verkauf Fertigarzneimittel an Vertriebsgesellschaft SG01</t>
+          <t>Sale of finished pharmaceuticals to distributor SG01</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Zuellig Pharma Singapore</t>
+          <t>Sale of finished goods to wholesaler Zuellig Pharma Singapore</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler DKSH Healthcare Asia</t>
+          <t>Sale of finished goods to wholesaler DKSH Healthcare Asia</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verkauf Fertigware an Grosshaendler Singapore MedSupply</t>
+          <t>Sale of finished goods to wholesaler Singapore MedSupply</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gutschrift Retoure Grosshandel</t>
+          <t>Credit note wholesale return</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lohnfertigungsgebuehr API-Produktion</t>
+          <t>Contract manufacturing fee API production</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sonstige Kosten - noch nicht klassifiziert</t>
+          <t>Other costs - not classified</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">

--- a/data/raw_erp_export.xlsx
+++ b/data/raw_erp_export.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
